--- a/jira_clone/agile_daily_tracker (2).xlsx
+++ b/jira_clone/agile_daily_tracker (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maamoun\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38F4ECD8-58AA-4198-816A-B1339C65C7C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C110AD99-75BC-4ADB-93AF-1D6920A0128B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="148">
   <si>
     <t>Date</t>
   </si>
@@ -530,24 +530,104 @@
     <t xml:space="preserve">`- delete ticket and delete tickets&gt;&gt; should affect the total story point. </t>
   </si>
   <si>
-    <t xml:space="preserve">what is affected by creating the totalStoryPoint and totalEndedStoryPoint : 
+    <t xml:space="preserve">`- move ticket to backlog </t>
+  </si>
+  <si>
+    <t xml:space="preserve">`- move ticket to sprint </t>
+  </si>
+  <si>
+    <t>commit : 242d8fb23d43b385ab646167a1bd352e1f81a7d7
+commit message : 5/7/2026-sprint1-Task-30</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>branch  : manage_ticket_page
+commit hash :395d5e0ca9b751e8bf99ac66f205ec356cac47b5
+commit message : 5/8/2026-sprint1-Task32</t>
+  </si>
+  <si>
+    <t>I do the change manually in frontEnd Then isee the network request and from it I know the controller and method , Then I set the Todo then I give the ai the prompt  for backEnd
+BackEnd : 15 min : AI &gt;&gt; P033.
+______________
+I am aware on what to change in front End so simply i update the state based on the new response and test i have some problem but i solve in debugging 
+FrontEnd : 10 min : Manually with debugging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">` front end BUG : we should return the sprint for the story point update because someone else can use the same app and update another sprint 
+so if we update the frontEnd based on just this ticket change so user will not show another user change. , 
+and this cannot be updated using wire because we have paging </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I do the change manually in frontEnd Then isee the network request and from it I know the controller and method , Then I set the Todo then I give the ai the prompt  for backEnd
+BackEnd : 20 min : AI &gt;&gt; P033. 18 min
+_______________
+</t>
+  </si>
+  <si>
+    <t>`- update createTicket Response in backEnd 
+- update the handler in js with enrich method
+I do prompt Task34 but it was not enough</t>
+  </si>
+  <si>
+    <t>Task 34</t>
+  </si>
+  <si>
+    <t>branch  : manage_ticket_page
+commit hash : f5dff0b41d8e95f198e6a71a2e5d9e65386c110c
+commit message : 5/8/2026-sprint1-[Task33-Task34]</t>
+  </si>
+  <si>
+    <t>what is affected by creating the totalStoryPoint and totalEndedStoryPoint : 
 BackEnd:
 - select total story point from the sprint not calculate : * update load Ticket Tracking, * update load Sprints. 
 - create ticket &gt;&gt; should affect the total story point. 
 - delete ticket &gt;&gt; should affect the total story point. 
 - update the story point for a ticket should affect the total story point (cannot update the story point for ticket in the end status for the current project).
 - move ticket to backlog 
-- move ticket to sprint </t>
-  </si>
-  <si>
-    <t xml:space="preserve">`- move ticket to backlog </t>
-  </si>
-  <si>
-    <t xml:space="preserve">`- move ticket to sprint </t>
-  </si>
-  <si>
-    <t>commit : 242d8fb23d43b385ab646167a1bd352e1f81a7d7
-commit message : 5/7/2026-sprint1-Task-30</t>
+- move ticket to sprint 
+- achieve ticket end status</t>
+  </si>
+  <si>
+    <t>`-achieve Ticket End status in Ticket Trackign Page 
+`-achieve Ticket End status in Manage Backlog Page</t>
+  </si>
+  <si>
+    <t>`- In Manage Ticket Tracking : do change and see the request to know the controller and method in  apex .
+`- in apex update the logic and the return response .
+`- in lwc update the state based on the return object</t>
+  </si>
+  <si>
+    <t>Update BackEnd Then create a anonymous apex call to check if I have the expected return response</t>
+  </si>
+  <si>
+    <t>Update FrontEnd based on the new return response</t>
+  </si>
+  <si>
+    <t>`-achieve Ticket End status in Ticket Trackign Page  and Manage Backlog: BACKEND</t>
+  </si>
+  <si>
+    <t>`-achieve Ticket End status in Ticket Trackign Page  and Manage Backlog: FRONTEND</t>
+  </si>
+  <si>
+    <t>Task 36 , 37</t>
+  </si>
+  <si>
+    <t>CREATE SEPARATE : 
+- CREATE TICKET WITH SPRINT IN SERVICE
+- CREATE TICKET WITHOUT SPRINT IN SERVICE 
+- CREATE TICKET FROM BACKLOG
+- CREATE TICKET FROM SPRINT</t>
+  </si>
+  <si>
+    <t>5 HOURS</t>
+  </si>
+  <si>
+    <t>TASK 41 DEVELOPMENT</t>
+  </si>
+  <si>
+    <t>1 HOURS</t>
   </si>
 </sst>
 </file>
@@ -663,7 +743,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -712,6 +792,9 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1944,7 +2027,7 @@
         <v>12</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="H28" s="6">
         <v>0.4</v>
@@ -2054,16 +2137,21 @@
       </c>
       <c r="J31" s="4"/>
       <c r="K31" s="21" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <v>46150</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="3"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="5" t="str">
-        <f>IF(C32="","",COUNTIF($C$2:C32,C32))</f>
-        <v/>
+      <c r="C32" s="4">
+        <v>1</v>
+      </c>
+      <c r="D32" s="5">
+        <v>31</v>
       </c>
       <c r="E32" s="21" t="s">
         <v>118</v>
@@ -2079,137 +2167,212 @@
       <c r="J32" s="4"/>
       <c r="K32" s="21"/>
     </row>
-    <row r="33" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="3"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="4"/>
+    <row r="33" spans="1:11" ht="190.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <v>46150</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C33" s="4">
+        <v>1</v>
+      </c>
       <c r="D33" s="5">
         <v>32</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G33" s="4"/>
-      <c r="H33" s="6"/>
+      <c r="G33" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="H33" s="6">
+        <v>0.3</v>
+      </c>
       <c r="I33" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-    </row>
-    <row r="34" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="3"/>
-      <c r="B34" s="4" t="str">
-        <f t="shared" ref="B30:B93" si="0">IF(A34="","",TEXT(A34,"dddd"))</f>
-        <v/>
-      </c>
-      <c r="C34" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="J33" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="K33" s="21" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="118.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <v>46150</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C34" s="4">
+        <v>1</v>
+      </c>
       <c r="D34" s="5">
         <v>33</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G34" s="4"/>
-      <c r="H34" s="6"/>
+      <c r="G34" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="H34" s="6">
+        <v>0.3</v>
+      </c>
       <c r="I34" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-    </row>
-    <row r="35" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="3"/>
-      <c r="B35" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="5" t="str">
-        <f>IF(C35="","",COUNTIF($C$2:C35,C35))</f>
-        <v/>
-      </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="4"/>
+        <v>46</v>
+      </c>
+      <c r="J34" s="4">
+        <v>34</v>
+      </c>
+      <c r="K34" s="21" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="177.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <v>46150</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C35" s="4">
+        <v>1</v>
+      </c>
+      <c r="D35" s="5">
+        <v>34</v>
+      </c>
+      <c r="E35" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="H35" s="22">
+        <v>1</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-    </row>
-    <row r="36" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="3"/>
-      <c r="B36" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="5" t="str">
-        <f>IF(C36="","",COUNTIF($C$2:C36,C36))</f>
-        <v/>
-      </c>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
+      <c r="K35" s="21" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <v>46150</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C36" s="4">
+        <v>1</v>
+      </c>
+      <c r="D36" s="5">
+        <v>35</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" s="21" t="s">
+        <v>138</v>
+      </c>
       <c r="H36" s="6"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
+      <c r="I36" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J36" s="21" t="s">
+        <v>143</v>
+      </c>
       <c r="K36" s="4"/>
     </row>
-    <row r="37" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="3"/>
-      <c r="B37" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="5" t="str">
-        <f>IF(C37="","",COUNTIF($C$2:C37,C37))</f>
-        <v/>
-      </c>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="4"/>
+    <row r="37" spans="1:11" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <v>46150</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C37" s="4">
+        <v>1</v>
+      </c>
+      <c r="D37" s="5">
+        <v>36</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H37" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
     </row>
-    <row r="38" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="3"/>
-      <c r="B38" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="5" t="str">
-        <f>IF(C38="","",COUNTIF($C$2:C38,C38))</f>
-        <v/>
-      </c>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="4"/>
+    <row r="38" spans="1:11" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <v>46150</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C38" s="4">
+        <v>1</v>
+      </c>
+      <c r="D38" s="5">
+        <v>37</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="F38" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="H38" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
     </row>
     <row r="39" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
-      <c r="B39" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C39" s="4"/>
-      <c r="D39" s="5" t="str">
-        <f>IF(C39="","",COUNTIF($C$2:C39,C39))</f>
-        <v/>
+      <c r="B39" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C39" s="4">
+        <v>1</v>
+      </c>
+      <c r="D39" s="5">
+        <v>38</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -2222,7 +2385,7 @@
     <row r="40" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B30:B93" si="0">IF(A40="","",TEXT(A40,"dddd"))</f>
         <v/>
       </c>
       <c r="C40" s="4"/>
@@ -2257,41 +2420,57 @@
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
     </row>
-    <row r="42" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="142.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
-      <c r="B42" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C42" s="4"/>
-      <c r="D42" s="5" t="str">
-        <f>IF(C42="","",COUNTIF($C$2:C42,C42))</f>
-        <v/>
-      </c>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
+      <c r="B42" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" s="4">
+        <v>2</v>
+      </c>
+      <c r="D42" s="5">
+        <v>41</v>
+      </c>
+      <c r="E42" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="G42" s="4"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="4"/>
+      <c r="H42" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
     </row>
     <row r="43" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
-      <c r="B43" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="C43" s="4"/>
-      <c r="D43" s="5" t="str">
-        <f>IF(C43="","",COUNTIF($C$2:C43,C43))</f>
-        <v/>
-      </c>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
+      <c r="B43" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="4">
+        <v>2</v>
+      </c>
+      <c r="D43" s="5">
+        <v>42</v>
+      </c>
+      <c r="E43" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="G43" s="4"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="4"/>
+      <c r="H43" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
     </row>
@@ -6430,7 +6609,7 @@
       </c>
       <c r="B3" s="16">
         <f>SUM('Daily Log'!H2:H248)</f>
-        <v>20.22</v>
+        <v>22.42</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -6439,7 +6618,7 @@
       </c>
       <c r="B4" s="17">
         <f>COUNTA('Daily Log'!E2:E248)</f>
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -6448,7 +6627,7 @@
       </c>
       <c r="B5" s="18">
         <f>SUMPRODUCT(('Daily Log'!A2:A248&lt;&gt;"")/COUNTIF('Daily Log'!A2:A248,'Daily Log'!A2:A248&amp;""))</f>
-        <v>4.0000000000000027</v>
+        <v>5.0000000000000053</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -6457,7 +6636,7 @@
       </c>
       <c r="B6" s="16">
         <f>IFERROR(B4/B5,0)</f>
-        <v>7.9999999999999947</v>
+        <v>7.5999999999999917</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -6466,7 +6645,7 @@
       </c>
       <c r="B7" s="16">
         <f>IFERROR(B3/B5,0)</f>
-        <v>5.0549999999999962</v>
+        <v>4.4839999999999955</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -6475,7 +6654,7 @@
       </c>
       <c r="B8" s="17">
         <f>COUNTIF('Daily Log'!I2:I248,"Done")</f>
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -6493,7 +6672,7 @@
       </c>
       <c r="B10" s="17">
         <f>COUNTIF('Daily Log'!I2:I248,"Blocked")</f>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -6502,7 +6681,7 @@
       </c>
       <c r="B11" s="19">
         <f>IFERROR(B8/B4,0)</f>
-        <v>0.625</v>
+        <v>0.65789473684210531</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -6526,7 +6705,7 @@
       </c>
       <c r="E14" s="16">
         <f>SUMIF('Daily Log'!C2:C248,1,'Daily Log'!H2:H248)</f>
-        <v>20.22</v>
+        <v>22.42</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -6551,7 +6730,7 @@
       </c>
       <c r="B16" s="16">
         <f>SUMIF('Daily Log'!F2:F248,A16,'Daily Log'!H2:H248)</f>
-        <v>14.499999999999998</v>
+        <v>16.700000000000003</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>105</v>
